--- a/Services/Fsel.System/Fsel.System.Api/Resources/ManagerReports/BaoCaoChuyenCan.xlsx
+++ b/Services/Fsel.System/Fsel.System.Api/Resources/ManagerReports/BaoCaoChuyenCan.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PhanPhuc\Fsel\fsel_src\Services\Fsel.Course\Fsel.Course.Lms.Api\Resources\ManagerReports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ExcelTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A2AD2C-4BEE-4D62-A5A1-32CD34ACF801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D28F7C7-B106-4CED-B968-52C2BE48FF23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7FD84967-D379-4295-B365-C4BAD0C1800B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="179021" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,6 +33,9 @@
     <t>Trường</t>
   </si>
   <si>
+    <t>[SchoolName]</t>
+  </si>
+  <si>
     <t>Tổng số học sinh</t>
   </si>
   <si>
@@ -72,44 +75,41 @@
     <t>Tổng số lần vào học</t>
   </si>
   <si>
-    <t>Thời gian bắt đầu học</t>
-  </si>
-  <si>
     <t>Ngày học gần nhất</t>
   </si>
   <si>
     <t>Ngày hết hạn</t>
   </si>
   <si>
-    <t>{0}</t>
+    <t>Ngày bắt đầu học</t>
+  </si>
+  <si>
+    <t>Ngày: {0}</t>
+  </si>
+  <si>
+    <t>Đến ngày: {0}</t>
+  </si>
+  <si>
+    <t>Từ ngày: {0}</t>
+  </si>
+  <si>
+    <t>Lớp: {0}</t>
+  </si>
+  <si>
+    <t>Khối: {0}</t>
   </si>
   <si>
     <t>Trạng thái: {0}</t>
   </si>
   <si>
-    <t>Khối: {0}</t>
-  </si>
-  <si>
     <t>Chương trình: {0}</t>
-  </si>
-  <si>
-    <t>Từ ngày: {0}</t>
-  </si>
-  <si>
-    <t>Đến ngày: {0}</t>
-  </si>
-  <si>
-    <t>Ngày: {0}</t>
-  </si>
-  <si>
-    <t>Lớp : {0}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -133,29 +133,15 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -261,30 +247,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -295,7 +277,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -615,164 +597,174 @@
   <dimension ref="A1:N6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5" customWidth="1"/>
-    <col min="8" max="8" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.5" customWidth="1"/>
+    <col min="1" max="1" width="11.75" customWidth="1"/>
+    <col min="2" max="2" width="17.625" customWidth="1"/>
+    <col min="3" max="3" width="17.125" customWidth="1"/>
+    <col min="4" max="4" width="10.625" customWidth="1"/>
+    <col min="5" max="5" width="16.625" customWidth="1"/>
+    <col min="6" max="6" width="10.75" customWidth="1"/>
+    <col min="7" max="7" width="21.625" customWidth="1"/>
+    <col min="8" max="8" width="22.375" customWidth="1"/>
+    <col min="9" max="9" width="13.875" customWidth="1"/>
+    <col min="10" max="10" width="14.75" customWidth="1"/>
+    <col min="11" max="12" width="18.125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="22.75" customWidth="1"/>
-    <col min="14" max="14" width="20.5" customWidth="1"/>
+    <col min="14" max="14" width="20.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
     </row>
-    <row r="2" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="3" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="L2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" s="5"/>
-      <c r="N2" s="4" t="s">
-        <v>24</v>
-      </c>
+      <c r="N2" s="2"/>
     </row>
     <row r="3" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
+      <c r="E3" s="1">
+        <v>120</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="5"/>
     </row>
     <row r="4" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
+      <c r="E4" s="1">
+        <v>100</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="5"/>
     </row>
     <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
+      <c r="E5" s="1">
+        <v>100</v>
+      </c>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="5"/>
     </row>
     <row r="6" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="8" t="s">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="B6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="D6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="E6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="F6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="G6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="H6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="I6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="J6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="K6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="M6" s="9" t="s">
+      <c r="L6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="N6" s="4" t="s">
         <v>17</v>
       </c>
     </row>
@@ -783,5 +775,6 @@
     <mergeCell ref="F5:G5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Services/Fsel.System/Fsel.System.Api/Resources/ManagerReports/BaoCaoChuyenCan.xlsx
+++ b/Services/Fsel.System/Fsel.System.Api/Resources/ManagerReports/BaoCaoChuyenCan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ExcelTemplate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PhanPhuc\Fsel\fsel_src\Services\Fsel.System\Fsel.System.Api\Resources\ManagerReports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D28F7C7-B106-4CED-B968-52C2BE48FF23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B1B238-9E33-410E-AF4E-9FDD5F6496B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7FD84967-D379-4295-B365-C4BAD0C1800B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7FD84967-D379-4295-B365-C4BAD0C1800B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>BÁO CÁO CHUYÊN CẦN (Academic &amp; Ielts)</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t>Chương trình: {0}</t>
+  </si>
+  <si>
+    <t>UserName</t>
   </si>
 </sst>
 </file>
@@ -594,25 +597,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE5CCA36-92B9-4B5C-976F-E001D77822BA}">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.75" customWidth="1"/>
-    <col min="2" max="2" width="17.625" customWidth="1"/>
-    <col min="3" max="3" width="17.125" customWidth="1"/>
-    <col min="4" max="4" width="10.625" customWidth="1"/>
-    <col min="5" max="5" width="16.625" customWidth="1"/>
-    <col min="6" max="6" width="10.75" customWidth="1"/>
-    <col min="7" max="7" width="21.625" customWidth="1"/>
-    <col min="8" max="8" width="22.375" customWidth="1"/>
-    <col min="9" max="9" width="13.875" customWidth="1"/>
-    <col min="10" max="10" width="14.75" customWidth="1"/>
-    <col min="11" max="12" width="18.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.75" customWidth="1"/>
-    <col min="14" max="14" width="20.375" customWidth="1"/>
+    <col min="1" max="2" width="11.75" customWidth="1"/>
+    <col min="3" max="3" width="17.625" customWidth="1"/>
+    <col min="4" max="4" width="17.125" customWidth="1"/>
+    <col min="5" max="5" width="10.625" customWidth="1"/>
+    <col min="6" max="6" width="16.625" customWidth="1"/>
+    <col min="7" max="7" width="10.75" customWidth="1"/>
+    <col min="8" max="8" width="21.625" customWidth="1"/>
+    <col min="9" max="9" width="22.375" customWidth="1"/>
+    <col min="10" max="10" width="13.875" customWidth="1"/>
+    <col min="11" max="11" width="14.75" customWidth="1"/>
+    <col min="12" max="13" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.75" customWidth="1"/>
+    <col min="15" max="15" width="20.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -629,150 +632,158 @@
       <c r="L1" s="9"/>
       <c r="M1" s="9"/>
       <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
     </row>
-    <row r="2" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="1"/>
+      <c r="H2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
     </row>
-    <row r="3" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="1">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1">
         <v>120</v>
       </c>
-      <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="5"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="5"/>
     </row>
-    <row r="4" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="1">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1">
         <v>100</v>
       </c>
-      <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="5"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="5"/>
     </row>
-    <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="1">
+      <c r="E5" s="1"/>
+      <c r="F5" s="1">
         <v>100</v>
       </c>
-      <c r="F5" s="11"/>
       <c r="G5" s="11"/>
-      <c r="H5" s="1"/>
+      <c r="H5" s="11"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="5"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="5"/>
     </row>
-    <row r="6" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="K6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="L6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="M6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="N6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="O6" s="4" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="G5:H5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Services/Fsel.System/Fsel.System.Api/Resources/ManagerReports/BaoCaoChuyenCan.xlsx
+++ b/Services/Fsel.System/Fsel.System.Api/Resources/ManagerReports/BaoCaoChuyenCan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PhanPhuc\Fsel\fsel_src\Services\Fsel.System\Fsel.System.Api\Resources\ManagerReports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Backend\fsel_src\Services\Fsel.System\Fsel.System.Api\Resources\ManagerReports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B1B238-9E33-410E-AF4E-9FDD5F6496B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345161E2-7FAD-47E8-B1BC-8A58A04621EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7FD84967-D379-4295-B365-C4BAD0C1800B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7FD84967-D379-4295-B365-C4BAD0C1800B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>BÁO CÁO CHUYÊN CẦN (Academic &amp; Ielts)</t>
   </si>
@@ -48,9 +48,6 @@
     <t>Họ và tên</t>
   </si>
   <si>
-    <t>Gmail</t>
-  </si>
-  <si>
     <t>Khối</t>
   </si>
   <si>
@@ -106,6 +103,12 @@
   </si>
   <si>
     <t>UserName</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Số điện thoại</t>
   </si>
 </sst>
 </file>
@@ -647,25 +650,25 @@
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O2" s="2"/>
     </row>
@@ -737,46 +740,46 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="K6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="L6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="M6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="N6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="M6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N6" s="4" t="s">
+      <c r="O6" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Services/Fsel.System/Fsel.System.Api/Resources/ManagerReports/BaoCaoChuyenCan.xlsx
+++ b/Services/Fsel.System/Fsel.System.Api/Resources/ManagerReports/BaoCaoChuyenCan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Backend\fsel_src\Services\Fsel.System\Fsel.System.Api\Resources\ManagerReports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345161E2-7FAD-47E8-B1BC-8A58A04621EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B1452C6-4775-4E72-85FD-633D32C29CAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7FD84967-D379-4295-B365-C4BAD0C1800B}"/>
   </bookViews>
@@ -27,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
-    <t>BÁO CÁO CHUYÊN CẦN (Academic &amp; Ielts)</t>
-  </si>
-  <si>
     <t>Trường</t>
   </si>
   <si>
@@ -109,6 +106,9 @@
   </si>
   <si>
     <t>Số điện thoại</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BÁO CÁO CHUYÊN CẦN </t>
   </si>
 </sst>
 </file>
@@ -620,7 +620,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -639,49 +639,49 @@
     </row>
     <row r="2" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
       <c r="F2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -695,14 +695,14 @@
     </row>
     <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -716,14 +716,14 @@
     </row>
     <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
@@ -737,49 +737,49 @@
     </row>
     <row r="6" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="K6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="L6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="M6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="M6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="N6" s="4" t="s">
+      <c r="O6" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
